--- a/data/s2/Aradas/archetypes/pop_archetypes_citizen.xlsx
+++ b/data/s2/Aradas/archetypes/pop_archetypes_citizen.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asier.divasson\Documents\GitHub\CogniCity\data\s2\Aradas\archetypes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asier.divasson\Documents\GitHub\CogniCity\data\Aradas\archetypes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7B247D6-94EC-40C2-8920-3073E9108BAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B1BEF6D-93C8-4E84-B2E3-F8176908639A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -790,12 +790,10 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="AE2" s="7">
-        <f>1215*0.974</f>
-        <v>1183.4100000000001</v>
+        <v>1215</v>
       </c>
       <c r="AF2" s="7">
-        <f>1156.6*0.974</f>
-        <v>1126.5283999999999</v>
+        <v>1156.5999999999999</v>
       </c>
       <c r="AG2" s="7">
         <v>0</v>
@@ -804,12 +802,10 @@
         <v>99999</v>
       </c>
       <c r="AI2" s="7">
-        <f>1872*0.974</f>
-        <v>1823.328</v>
+        <v>1872</v>
       </c>
       <c r="AJ2" s="7">
-        <f>1182*0.974</f>
-        <v>1151.268</v>
+        <v>1182</v>
       </c>
       <c r="AK2" s="7">
         <v>0</v>
@@ -911,12 +907,10 @@
         <v>7.1999999999999995E-2</v>
       </c>
       <c r="AE3" s="7">
-        <f>1215*0.974</f>
-        <v>1183.4100000000001</v>
+        <v>1215</v>
       </c>
       <c r="AF3" s="7">
-        <f>1156.6*0.974</f>
-        <v>1126.5283999999999</v>
+        <v>1156.5999999999999</v>
       </c>
       <c r="AG3" s="7">
         <v>0</v>
@@ -925,12 +919,10 @@
         <v>99999</v>
       </c>
       <c r="AI3" s="7">
-        <f>1872*0.974</f>
-        <v>1823.328</v>
+        <v>1872</v>
       </c>
       <c r="AJ3" s="7">
-        <f>1182*0.974</f>
-        <v>1151.268</v>
+        <v>1182</v>
       </c>
       <c r="AK3" s="7">
         <v>0</v>
@@ -1031,12 +1023,10 @@
         <v>4.2000000000000003E-2</v>
       </c>
       <c r="AE4" s="7">
-        <f>2708*0.974</f>
-        <v>2637.5920000000001</v>
+        <v>2708</v>
       </c>
       <c r="AF4" s="7">
-        <f>1156.6*0.974</f>
-        <v>1126.5283999999999</v>
+        <v>1156.5999999999999</v>
       </c>
       <c r="AG4" s="7">
         <v>0</v>
@@ -1045,12 +1035,10 @@
         <v>99999</v>
       </c>
       <c r="AI4" s="7">
-        <f>1872*0.974</f>
-        <v>1823.328</v>
+        <v>1872</v>
       </c>
       <c r="AJ4" s="7">
-        <f>1182*0.974</f>
-        <v>1151.268</v>
+        <v>1182</v>
       </c>
       <c r="AK4" s="7">
         <v>0</v>
@@ -1109,7 +1097,6 @@
         <v>240</v>
       </c>
       <c r="Q5" s="8">
-        <f>1-0.0670582476749878</f>
         <v>0.9329417523250122</v>
       </c>
       <c r="R5" s="11">
@@ -1152,12 +1139,10 @@
         <v>6.7000000000000004E-2</v>
       </c>
       <c r="AE5" s="7">
-        <f>1215*0.974</f>
-        <v>1183.4100000000001</v>
+        <v>1215</v>
       </c>
       <c r="AF5" s="7">
-        <f>1156.6*0.974</f>
-        <v>1126.5283999999999</v>
+        <v>1156.5999999999999</v>
       </c>
       <c r="AG5" s="7">
         <v>0</v>
@@ -1166,12 +1151,10 @@
         <v>99999</v>
       </c>
       <c r="AI5" s="7">
-        <f>1872*0.974</f>
-        <v>1823.328</v>
+        <v>1872</v>
       </c>
       <c r="AJ5" s="7">
-        <f>1182*0.974</f>
-        <v>1151.268</v>
+        <v>1182</v>
       </c>
       <c r="AK5" s="7">
         <v>0</v>
@@ -1272,12 +1255,10 @@
         <v>4.2000000000000003E-2</v>
       </c>
       <c r="AE6" s="7">
-        <f>1253*0.974</f>
-        <v>1220.422</v>
+        <v>1253</v>
       </c>
       <c r="AF6" s="7">
-        <f>1155*0.974</f>
-        <v>1124.97</v>
+        <v>1155</v>
       </c>
       <c r="AG6" s="7">
         <v>0</v>
@@ -1286,12 +1267,10 @@
         <v>99999</v>
       </c>
       <c r="AI6" s="7">
-        <f>1872*0.974</f>
-        <v>1823.328</v>
+        <v>1872</v>
       </c>
       <c r="AJ6" s="7">
-        <f>1182*0.974</f>
-        <v>1151.268</v>
+        <v>1182</v>
       </c>
       <c r="AK6" s="7">
         <v>0</v>
@@ -1299,9 +1278,6 @@
       <c r="AL6" s="7">
         <v>99999</v>
       </c>
-    </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="Q9" s="3"/>
     </row>
     <row r="10" spans="1:38" x14ac:dyDescent="0.3">
       <c r="Q10" s="3"/>
